--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -672,27 +672,27 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -720,12 +720,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -816,27 +816,27 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -864,12 +864,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -958,27 +958,27 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -1006,12 +1006,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1102,27 +1102,27 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -1150,12 +1150,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1244,27 +1244,27 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1292,12 +1292,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1388,27 +1388,27 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1436,12 +1436,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1530,27 +1530,27 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1578,12 +1578,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1674,27 +1674,27 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1722,12 +1722,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1816,27 +1816,27 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1864,12 +1864,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1960,27 +1960,27 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2008,12 +2008,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -2102,27 +2102,27 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2246,27 +2246,27 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -2294,12 +2294,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2388,27 +2388,27 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2436,12 +2436,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2532,27 +2532,27 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2580,12 +2580,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2674,27 +2674,27 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2722,12 +2722,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2818,27 +2818,27 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2866,12 +2866,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2960,27 +2960,27 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3008,12 +3008,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -3104,27 +3104,27 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3152,12 +3152,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -3246,27 +3246,27 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -3294,12 +3294,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3390,27 +3390,27 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3438,12 +3438,12 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3532,27 +3532,27 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -3580,12 +3580,12 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3676,27 +3676,27 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -3724,12 +3724,12 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3818,27 +3818,27 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -3866,12 +3866,12 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3962,27 +3962,27 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -4010,12 +4010,12 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -4104,27 +4104,27 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -4152,12 +4152,12 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -4248,27 +4248,27 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -4296,12 +4296,12 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -4390,27 +4390,27 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -4438,12 +4438,12 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -4534,27 +4534,27 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -4582,12 +4582,12 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4676,27 +4676,27 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -4724,12 +4724,12 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4820,27 +4820,27 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -4868,12 +4868,12 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4962,27 +4962,27 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -5010,12 +5010,12 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -5106,27 +5106,27 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -5154,12 +5154,12 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -5248,27 +5248,27 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -5296,12 +5296,12 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -5392,27 +5392,27 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -5440,12 +5440,12 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -5534,27 +5534,27 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -5582,12 +5582,12 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5678,27 +5678,27 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -5726,12 +5726,12 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5820,27 +5820,27 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -5868,12 +5868,12 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -5964,27 +5964,27 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -6012,12 +6012,12 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -6106,27 +6106,27 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -6250,27 +6250,27 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
@@ -6298,12 +6298,12 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -6392,27 +6392,27 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -6440,12 +6440,12 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -6536,27 +6536,27 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Imaging</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>logistic regression (with covariates)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -6584,12 +6584,12 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>HRC;1000G</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>European ancestry</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>

--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AT43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Imputation_simple2</t>
+          <t>Imputation</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -678,194 +678,90 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>['Meta-analysis', 'Discovery', 'IGAP']</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>['Imaging']</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['logistic regression (with covariates)']</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>SNP-based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>['74046']</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['1000 Genomes', 'Haplotype Reference Consortium', 'TOPMed', 'UK10K']</t>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>['European', '1000 Genomes EUR', 'ADGC', 'ADSP', 'IGAP']</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>eQTL association</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1.51e-07</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
           <t>30448613</t>
@@ -874,17 +770,5059 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>30448613_table2.xlsx</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>2.05e-06</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>rs6733839</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1.83e-11</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>6.960000000000001e-09</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1.71e-08</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1.53e-17</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>3.53e-09</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>TRIM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>TRIM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>4.150000000000001e-09</v>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.115</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>1.58e-08</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>3.77e-08</v>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00021</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>6.07e-05</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>3.68e-06</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>6.86e-18</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1.18e-17</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00033</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>2.31e-06</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00034</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>1.07e-07</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>8.130000000000001e-05</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>2.34e-12</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL38" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00039</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1.15e-06</v>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL40" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00041</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>1.59e-06</v>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL42" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00042</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
         </is>
       </c>
     </row>

--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -685,7 +685,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -767,7 +767,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR2" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -809,7 +813,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -822,7 +826,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -832,12 +836,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -848,7 +852,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -889,7 +893,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR3" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -931,7 +939,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -944,7 +952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -954,12 +962,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -970,7 +978,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1013,7 +1021,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR4" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1055,7 +1067,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1068,7 +1080,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1078,12 +1090,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1094,7 +1106,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1135,7 +1147,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR5" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1177,7 +1193,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1190,7 +1206,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1200,12 +1216,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1216,7 +1232,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1259,7 +1275,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR6" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1301,7 +1321,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1314,7 +1334,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1324,12 +1344,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1340,7 +1360,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1381,7 +1401,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR7" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1423,7 +1447,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1436,7 +1460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1446,12 +1470,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1462,7 +1486,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1505,7 +1529,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR8" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1547,7 +1575,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1560,7 +1588,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1570,12 +1598,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1586,7 +1614,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1627,7 +1655,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR9" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1669,7 +1701,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1682,7 +1714,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1692,12 +1724,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1708,7 +1740,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1751,7 +1783,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR10" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1793,7 +1829,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1806,7 +1842,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1816,12 +1852,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1832,7 +1868,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1873,7 +1909,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR11" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -1915,7 +1955,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1928,7 +1968,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1938,12 +1978,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1954,7 +1994,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1997,7 +2037,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR12" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2039,7 +2083,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2052,7 +2096,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2062,12 +2106,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2078,7 +2122,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2119,7 +2163,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR13" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2161,7 +2209,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2174,7 +2222,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2184,12 +2232,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2200,7 +2248,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2243,7 +2291,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR14" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2285,7 +2337,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2298,7 +2350,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2308,12 +2360,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2324,7 +2376,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2365,7 +2417,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR15" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2407,7 +2463,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2420,7 +2476,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2430,12 +2486,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2446,7 +2502,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2489,7 +2545,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR16" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2531,7 +2591,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2544,7 +2604,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2554,12 +2614,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2570,7 +2630,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2611,7 +2671,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR17" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2653,7 +2717,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2666,7 +2730,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2676,12 +2740,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2692,7 +2756,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2735,7 +2799,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR18" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2777,7 +2845,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2790,7 +2858,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2800,12 +2868,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2816,7 +2884,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2857,7 +2925,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR19" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -2899,7 +2971,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2912,7 +2984,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2922,12 +2994,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2938,7 +3010,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2981,7 +3053,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR20" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3023,7 +3099,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3036,7 +3112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -3046,12 +3122,12 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3062,7 +3138,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3103,7 +3179,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR21" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3145,7 +3225,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3158,7 +3238,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -3168,12 +3248,12 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3184,7 +3264,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3227,7 +3307,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR22" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3269,7 +3353,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -3282,7 +3366,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -3292,12 +3376,12 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3308,7 +3392,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3349,7 +3433,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR23" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3391,7 +3479,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -3404,7 +3492,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -3414,12 +3502,12 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3430,7 +3518,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3473,7 +3561,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR24" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3515,7 +3607,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -3528,7 +3620,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3538,12 +3630,12 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3554,7 +3646,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3595,7 +3687,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR25" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3637,7 +3733,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -3650,7 +3746,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -3660,12 +3756,12 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3676,7 +3772,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3719,7 +3815,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR26" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3761,7 +3861,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -3774,7 +3874,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3784,12 +3884,12 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3800,7 +3900,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3841,7 +3941,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR27" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -3883,7 +3987,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -3896,7 +4000,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3906,12 +4010,12 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3922,7 +4026,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3965,7 +4069,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR28" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4007,7 +4115,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4020,7 +4128,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -4030,12 +4138,12 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4046,7 +4154,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4087,7 +4195,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR29" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4129,7 +4241,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -4142,7 +4254,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -4152,12 +4264,12 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4168,7 +4280,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4211,7 +4323,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR30" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4253,7 +4369,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -4266,7 +4382,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -4276,12 +4392,12 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4292,7 +4408,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4333,7 +4449,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR31" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4375,7 +4495,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -4388,7 +4508,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -4398,12 +4518,12 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4414,7 +4534,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4457,7 +4577,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR32" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4499,7 +4623,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -4512,7 +4636,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -4522,12 +4646,12 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4538,7 +4662,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4579,7 +4703,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR33" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4621,7 +4749,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -4634,7 +4762,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -4644,12 +4772,12 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -4660,7 +4788,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4703,7 +4831,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR34" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4745,7 +4877,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -4758,7 +4890,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -4768,12 +4900,12 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -4784,7 +4916,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4825,7 +4957,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR35" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4867,7 +5003,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -4880,7 +5016,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -4890,12 +5026,12 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -4906,7 +5042,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4949,7 +5085,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR36" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -4991,7 +5131,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -5004,7 +5144,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -5014,12 +5154,12 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5030,7 +5170,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5071,7 +5211,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR37" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -5113,7 +5257,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -5126,7 +5270,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -5136,12 +5280,12 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -5152,7 +5296,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5195,7 +5339,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR38" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -5237,7 +5385,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -5250,7 +5398,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -5260,12 +5408,12 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -5276,7 +5424,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5317,7 +5465,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR39" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -5359,7 +5511,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -5372,7 +5524,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -5382,12 +5534,12 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5398,7 +5550,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5441,7 +5593,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR40" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -5483,7 +5639,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -5496,7 +5652,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -5506,12 +5662,12 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -5522,7 +5678,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5563,7 +5719,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR41" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -5605,7 +5765,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -5618,7 +5778,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -5628,12 +5788,12 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -5644,7 +5804,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5687,7 +5847,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR42" t="inlineStr">
         <is>
           <t>Table 2</t>
@@ -5729,7 +5893,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A + o + - + e +   + D + P + M + G + t + n + + + y + s + r + i + l + I + v + a + c</t>
+          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -5742,7 +5906,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>S + I + H + D + C + E + A + G + B + P + N + + +   + R + U + K</t>
+          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5752,12 +5916,12 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1 + C + O + o +   + e + K + H + P + M + R + 0 + t + u + G + n + d + p + T + y + + + s + r + U + i + l + a + f + m + c</t>
+          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1 + E + C + A + o + e +   + D + P + R + 0 + S + G + u + n + p + + + s + U + r + I + a + m</t>
+          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -5768,7 +5932,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>a + D + z + h + A + ' + m + d +   + + + s + e + r + i + l</t>
+          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5809,7 +5973,11 @@
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
       <c r="AR43" t="inlineStr">
         <is>
           <t>Table 2</t>

--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -685,7 +685,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -836,12 +836,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -939,7 +939,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -962,12 +962,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1067,7 +1067,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1193,7 +1193,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1216,12 +1216,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1321,7 +1321,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1344,12 +1344,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1575,7 +1575,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1598,12 +1598,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1701,7 +1701,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1724,12 +1724,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1829,7 +1829,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1852,12 +1852,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1978,12 +1978,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2083,7 +2083,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2232,12 +2232,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2360,12 +2360,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2463,7 +2463,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2591,7 +2591,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2614,12 +2614,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2717,7 +2717,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2845,7 +2845,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2868,12 +2868,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2971,7 +2971,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2994,12 +2994,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -3122,12 +3122,12 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3225,7 +3225,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -3248,12 +3248,12 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3353,7 +3353,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -3376,12 +3376,12 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3479,7 +3479,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -3502,12 +3502,12 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3607,7 +3607,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3630,12 +3630,12 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3733,7 +3733,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -3756,12 +3756,12 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3861,7 +3861,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3884,12 +3884,12 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3987,7 +3987,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -4010,12 +4010,12 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4115,7 +4115,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -4138,12 +4138,12 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4241,7 +4241,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -4264,12 +4264,12 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4369,7 +4369,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -4392,12 +4392,12 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4495,7 +4495,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -4518,12 +4518,12 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4623,7 +4623,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -4772,12 +4772,12 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4877,7 +4877,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -4900,12 +4900,12 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -5026,12 +5026,12 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5131,7 +5131,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -5154,12 +5154,12 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5257,7 +5257,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -5280,12 +5280,12 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5385,7 +5385,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -5408,12 +5408,12 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5511,7 +5511,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -5534,12 +5534,12 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5639,7 +5639,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -5662,12 +5662,12 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5765,7 +5765,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -5788,12 +5788,12 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5893,7 +5893,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>P + e + M + D + o + l + A + - + y + a + s + v + r + i + t +   + + + I + c + n + G</t>
+          <t>o + + + D + M + i + c +   + e + a + G + r + A + - + t + n + P + s + v + l + y + I</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>R + U + P + C + N + A + B +   + S + E + G + + + H + K + I + D</t>
+          <t>+ + I + H + U + P + N + B + D + R +   + S + E + A + G + C + K</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5916,12 +5916,12 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>R + P + u + e + M + o + l + 1 + d + H + O + y + a + s + r + i + t + T +   + f + + + K + p + U + c + C + n + 0 + m + G</t>
+          <t>0 + o + + + u + U + M + d + R + i + p + c +   + e + a + r + G + C + T + m + K + t + n + P + 1 + s + l + y + H + f + O</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>R + P + u + e + D + o + A + 1 + E + a + s + r +   + + + I + p + U + C + n + 0 + m + S + G</t>
+          <t>0 + o + + + U + u + D + R + S + p +   + e + a + G + r + C + A + m + n + P + 1 + s + E + I</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>s + r + i + l + z + A + h +   + m + + + d + e + D + a + '</t>
+          <t>m + + + z + h + D + i + s + d +   + e + a + l + A + r + '</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">

--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT43"/>
+  <dimension ref="A1:AU43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,85 +564,90 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>P-value note</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>BP(Position)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>RA 1(Reported Allele 1)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>RA 2(Reported Allele 2)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Note on alleles and AF</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ReportedAF(MAF)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>AFincases</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>AFincontrols</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Effect Size Type (OR or Beta)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>EffectSize(altvsref)</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>95%ConfidenceInterval</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Confirmed affected genes, causal variants, evidence</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Genome build (hg18/hg37/hg38)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Pubmed PMID</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>PMCID</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Table Ref in paper</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Table links</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>LocusName</t>
         </is>
@@ -669,7 +674,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Probe set: 11719631_s_at; closest gene: BIN1</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -702,12 +711,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -737,11 +746,19 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>rs6733839</t>
@@ -752,41 +769,46 @@
       <c r="AC2" t="n">
         <v>1.51e-07</v>
       </c>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr">
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
@@ -813,7 +835,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Probe set: 11719631_s_at; closest gene: BIN1</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -846,12 +872,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -881,11 +907,15 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>rs6733839</t>
@@ -896,39 +926,44 @@
       <c r="AC3" t="n">
         <v>0.28</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr">
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
@@ -955,7 +990,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Probe set: 11746895_a_at; closest gene: BIN1</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -988,12 +1027,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1023,11 +1062,19 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>rs6733839</t>
@@ -1038,41 +1085,46 @@
       <c r="AC4" t="n">
         <v>2.05e-06</v>
       </c>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr">
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr">
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
@@ -1099,7 +1151,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Probe set: 11746895_a_at; closest gene: BIN1</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1132,12 +1188,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1167,11 +1223,15 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>BIN1</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>rs6733839</t>
@@ -1182,39 +1242,44 @@
       <c r="AC5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr">
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
@@ -1241,7 +1306,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Probe set: 11730933_a_at; closest gene: HLA-DRB5</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1274,12 +1343,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1309,11 +1378,19 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>rs111418223</t>
@@ -1324,41 +1401,46 @@
       <c r="AC6" t="n">
         <v>1.83e-11</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr">
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>0.12</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr">
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
@@ -1385,7 +1467,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Probe set: 11730933_a_at; closest gene: HLA-DRB5</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1418,12 +1504,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1453,11 +1539,15 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>rs111418223</t>
@@ -1468,39 +1558,44 @@
       <c r="AC7" t="n">
         <v>0.91</v>
       </c>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr">
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
@@ -1527,7 +1622,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Probe set: 11750187_a_at; closest gene: HLA-DRB5</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1560,12 +1659,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1595,11 +1694,19 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>rs111418223</t>
@@ -1610,41 +1717,46 @@
       <c r="AC8" t="n">
         <v>6.960000000000001e-09</v>
       </c>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr">
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>0.114</v>
       </c>
-      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr">
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
@@ -1671,7 +1783,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Probe set: 11750187_a_at; closest gene: HLA-DRB5</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1704,12 +1820,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1739,11 +1855,15 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>rs111418223</t>
@@ -1754,39 +1874,44 @@
       <c r="AC9" t="n">
         <v>0.68</v>
       </c>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr">
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
@@ -1813,7 +1938,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Probe set: 11751668_a_at; closest gene: HLA-DRB5</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1846,12 +1975,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1881,11 +2010,19 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>rs111418223</t>
@@ -1896,41 +2033,46 @@
       <c r="AC10" t="n">
         <v>1.71e-08</v>
       </c>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr">
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>0.119</v>
       </c>
-      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr">
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
@@ -1957,7 +2099,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Probe set: 11751668_a_at; closest gene: HLA-DRB5</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1990,12 +2136,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2025,11 +2171,15 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>rs111418223</t>
@@ -2040,39 +2190,44 @@
       <c r="AC11" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr">
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
@@ -2099,7 +2254,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Probe set: 11722909_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2132,12 +2291,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2167,11 +2326,19 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -2182,41 +2349,46 @@
       <c r="AC12" t="n">
         <v>1.53e-17</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr">
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>0.177</v>
       </c>
-      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr">
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr">
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t>GATS</t>
         </is>
@@ -2243,7 +2415,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Probe set: 11722909_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2276,12 +2452,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2311,11 +2487,15 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>GATS</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -2326,39 +2506,44 @@
       <c r="AC13" t="n">
         <v>0.53</v>
       </c>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr">
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr">
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>GATS</t>
         </is>
@@ -2385,7 +2570,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Probe set: 11736388_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2418,12 +2607,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2453,11 +2642,19 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>TRIM4</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -2468,41 +2665,46 @@
       <c r="AC14" t="n">
         <v>3.53e-09</v>
       </c>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr">
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL14" t="n">
+      <c r="AM14" t="n">
         <v>-0.129</v>
       </c>
-      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr">
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr">
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>TRIM4</t>
         </is>
@@ -2529,7 +2731,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Probe set: 11736388_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2562,12 +2768,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2597,11 +2803,15 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>TRIM4</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -2612,39 +2822,44 @@
       <c r="AC15" t="n">
         <v>0.95</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr">
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr">
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
         <is>
           <t>TRIM4</t>
         </is>
@@ -2671,7 +2886,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Probe set: 11743311_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2704,12 +2923,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2739,11 +2958,19 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -2754,41 +2981,46 @@
       <c r="AC16" t="n">
         <v>4.150000000000001e-09</v>
       </c>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr">
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL16" t="n">
+      <c r="AM16" t="n">
         <v>-0.115</v>
       </c>
-      <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr">
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr">
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>PILRB</t>
         </is>
@@ -2815,7 +3047,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Probe set: 11743311_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2848,12 +3084,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2883,11 +3119,15 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -2898,39 +3138,44 @@
       <c r="AC17" t="n">
         <v>0.85</v>
       </c>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr">
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr">
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>PILRB</t>
         </is>
@@ -2957,7 +3202,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Probe set: 11730023 s at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -2990,12 +3239,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3025,11 +3274,19 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3040,41 +3297,46 @@
       <c r="AC18" t="n">
         <v>1.58e-08</v>
       </c>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr">
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL18" t="n">
+      <c r="AM18" t="n">
         <v>-0.107</v>
       </c>
-      <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr">
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr">
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>PILRB</t>
         </is>
@@ -3101,7 +3363,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Probe set: 11730023 s at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3134,12 +3400,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3169,11 +3435,15 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3184,39 +3454,44 @@
       <c r="AC19" t="n">
         <v>0.78</v>
       </c>
-      <c r="AD19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr">
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr">
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>PILRB</t>
         </is>
@@ -3243,7 +3518,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Probe set: 11730022_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3276,12 +3555,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3311,11 +3590,19 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3326,41 +3613,46 @@
       <c r="AC20" t="n">
         <v>3.77e-08</v>
       </c>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr">
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
         <v>-0.128</v>
       </c>
-      <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr">
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr">
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
         <is>
           <t>PILRB</t>
         </is>
@@ -3387,7 +3679,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Probe set: 11730022_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3420,12 +3716,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3455,11 +3751,15 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PILRB</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3470,39 +3770,44 @@
       <c r="AC21" t="n">
         <v>0.89</v>
       </c>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr">
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr">
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AT21" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
         <is>
           <t>PILRB</t>
         </is>
@@ -3529,7 +3834,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Probe set: 11760665_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3562,12 +3871,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3597,11 +3906,19 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3612,41 +3929,46 @@
       <c r="AC22" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr">
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL22" t="n">
+      <c r="AM22" t="n">
         <v>0.147</v>
       </c>
-      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr">
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr">
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="AU22" t="inlineStr">
         <is>
           <t>ZKSCAN1</t>
         </is>
@@ -3673,7 +3995,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Probe set: 11760665_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3706,12 +4032,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3741,11 +4067,15 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3756,39 +4086,44 @@
       <c r="AC23" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr">
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr">
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
         <is>
           <t>ZKSCAN1</t>
         </is>
@@ -3815,7 +4150,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Probe set: 11730247_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3848,12 +4187,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3883,11 +4222,19 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -3898,41 +4245,46 @@
       <c r="AC24" t="n">
         <v>6.07e-05</v>
       </c>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr">
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr">
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr">
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AU24" t="inlineStr">
         <is>
           <t>PVRIG</t>
         </is>
@@ -3959,7 +4311,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Probe set: 11730247_a_at; closest gene: ZCWPW1</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -3992,12 +4348,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4027,11 +4383,15 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
           <t>rs1476679</t>
@@ -4042,39 +4402,44 @@
       <c r="AC25" t="n">
         <v>0.82</v>
       </c>
-      <c r="AD25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr">
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr">
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
+      <c r="AT25" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>PVRIG</t>
         </is>
@@ -4101,7 +4466,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Probe set: 11755327 s at; closest gene: EPHA1</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4134,12 +4503,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4169,11 +4538,19 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
           <t>rs11771145</t>
@@ -4184,41 +4561,46 @@
       <c r="AC26" t="n">
         <v>3.68e-06</v>
       </c>
-      <c r="AD26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr">
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>0.109</v>
       </c>
-      <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr">
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr">
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AT26" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr">
+      <c r="AU26" t="inlineStr">
         <is>
           <t>LOC154761</t>
         </is>
@@ -4245,7 +4627,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Probe set: 11755327 s at; closest gene: EPHA1</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4278,12 +4664,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4313,11 +4699,15 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
           <t>rs11771145</t>
@@ -4328,39 +4718,44 @@
       <c r="AC27" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr">
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr">
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AT27" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
         <is>
           <t>LOC154761</t>
         </is>
@@ -4387,7 +4782,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Probe set: 11720981_a_at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4420,12 +4819,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4455,11 +4854,19 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -4470,41 +4877,46 @@
       <c r="AC28" t="n">
         <v>6.86e-18</v>
       </c>
-      <c r="AD28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr">
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>0.114</v>
       </c>
-      <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr">
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr">
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS28" t="inlineStr">
+      <c r="AT28" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr">
+      <c r="AU28" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
@@ -4531,7 +4943,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Probe set: 11720981_a_at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4564,12 +4980,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4599,11 +5015,15 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -4614,39 +5034,44 @@
       <c r="AC29" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr">
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr">
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AT29" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr">
+      <c r="AU29" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
@@ -4673,7 +5098,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Probe set: 11720982 s at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4706,12 +5135,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4741,11 +5170,19 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -4756,41 +5193,46 @@
       <c r="AC30" t="n">
         <v>1.18e-17</v>
       </c>
-      <c r="AD30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr">
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr">
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr">
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AT30" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr">
+      <c r="AU30" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
@@ -4817,7 +5259,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Probe set: 11720982 s at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4850,12 +5296,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4885,11 +5331,15 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -4900,39 +5350,44 @@
       <c r="AC31" t="n">
         <v>0.91</v>
       </c>
-      <c r="AD31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr">
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr">
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr">
+      <c r="AT31" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr">
+      <c r="AU31" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
@@ -4959,7 +5414,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Probe set: 11720980_a_at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -4992,12 +5451,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5027,11 +5486,19 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -5042,41 +5509,46 @@
       <c r="AC32" t="n">
         <v>7.33e-12</v>
       </c>
-      <c r="AD32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr">
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>0.094</v>
       </c>
-      <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr">
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr">
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AT32" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
+      <c r="AU32" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
@@ -5103,7 +5575,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Probe set: 11720980_a_at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5136,12 +5612,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5171,11 +5647,15 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -5186,39 +5666,44 @@
       <c r="AC33" t="n">
         <v>0.47</v>
       </c>
-      <c r="AD33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr">
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr">
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AT33" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr">
+      <c r="AU33" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
@@ -5245,7 +5730,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Probe set: 11723344_at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5278,12 +5767,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5313,11 +5802,19 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -5328,41 +5825,46 @@
       <c r="AC34" t="n">
         <v>2.31e-06</v>
       </c>
-      <c r="AD34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr">
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr">
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr">
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
+      <c r="AT34" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT34" t="inlineStr">
+      <c r="AU34" t="inlineStr">
         <is>
           <t>TRIM35</t>
         </is>
@@ -5389,7 +5891,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Probe set: 11723344_at; closest gene: PTK2B</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5422,12 +5928,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5457,11 +5963,15 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
       <c r="Z35" t="inlineStr">
         <is>
           <t>rs28834970</t>
@@ -5472,39 +5982,44 @@
       <c r="AC35" t="n">
         <v>0.45</v>
       </c>
-      <c r="AD35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr">
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr">
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AT35" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT35" t="inlineStr">
+      <c r="AU35" t="inlineStr">
         <is>
           <t>TRIM35</t>
         </is>
@@ -5531,7 +6046,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Probe set: 11725151_at; closest gene: CELF1</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5564,12 +6083,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5599,11 +6118,19 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr">
         <is>
           <t>rs10838725</t>
@@ -5614,41 +6141,46 @@
       <c r="AC36" t="n">
         <v>1.07e-07</v>
       </c>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr">
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
         <v>0.14</v>
       </c>
-      <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr">
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr">
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
+      <c r="AT36" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT36" t="inlineStr">
+      <c r="AU36" t="inlineStr">
         <is>
           <t>MYBPC3</t>
         </is>
@@ -5675,7 +6207,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Probe set: 11725151_at; closest gene: CELF1</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5708,12 +6244,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5743,11 +6279,15 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
       <c r="Z37" t="inlineStr">
         <is>
           <t>rs10838725</t>
@@ -5758,39 +6298,44 @@
       <c r="AC37" t="n">
         <v>8.130000000000001e-05</v>
       </c>
-      <c r="AD37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr">
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr">
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS37" t="inlineStr">
+      <c r="AT37" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT37" t="inlineStr">
+      <c r="AU37" t="inlineStr">
         <is>
           <t>MYBPC3</t>
         </is>
@@ -5817,7 +6362,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Probe set: 11716846_a_at; closest gene: MS4A6A</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5850,12 +6399,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5885,11 +6434,19 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
       <c r="Z38" t="inlineStr">
         <is>
           <t>rs983392</t>
@@ -5900,41 +6457,46 @@
       <c r="AC38" t="n">
         <v>2.34e-12</v>
       </c>
-      <c r="AD38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr">
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL38" t="n">
+      <c r="AM38" t="n">
         <v>-0.082</v>
       </c>
-      <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr">
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr">
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS38" t="inlineStr">
+      <c r="AT38" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT38" t="inlineStr">
+      <c r="AU38" t="inlineStr">
         <is>
           <t>MS4A6A</t>
         </is>
@@ -5961,7 +6523,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Probe set: 11716846_a_at; closest gene: MS4A6A</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -5994,12 +6560,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6029,11 +6595,15 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
           <t>rs983392</t>
@@ -6044,39 +6614,44 @@
       <c r="AC39" t="n">
         <v>0.00497</v>
       </c>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr">
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr">
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS39" t="inlineStr">
+      <c r="AT39" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT39" t="inlineStr">
+      <c r="AU39" t="inlineStr">
         <is>
           <t>MS4A6A</t>
         </is>
@@ -6103,7 +6678,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Probe set: 11751570_a_at; closest gene: MS4A6A</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -6136,12 +6715,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6171,11 +6750,19 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr">
         <is>
           <t>rs983392</t>
@@ -6186,41 +6773,46 @@
       <c r="AC40" t="n">
         <v>1.15e-06</v>
       </c>
-      <c r="AD40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr">
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL40" t="n">
+      <c r="AM40" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr">
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr">
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS40" t="inlineStr">
+      <c r="AT40" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT40" t="inlineStr">
+      <c r="AU40" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
@@ -6247,7 +6839,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Probe set: 11751570_a_at; closest gene: MS4A6A</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -6280,12 +6876,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6315,11 +6911,15 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr">
         <is>
           <t>rs983392</t>
@@ -6330,39 +6930,44 @@
       <c r="AC41" t="n">
         <v>0.85</v>
       </c>
-      <c r="AD41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr">
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr">
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS41" t="inlineStr">
+      <c r="AT41" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT41" t="inlineStr">
+      <c r="AU41" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
@@ -6389,7 +6994,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Probe set: 11732865_a_at; closest gene: MS4A6A</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -6422,12 +7031,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6457,11 +7066,19 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>rs983392</t>
@@ -6472,41 +7089,46 @@
       <c r="AC42" t="n">
         <v>1.59e-06</v>
       </c>
-      <c r="AD42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>eQTL association P-value</t>
+        </is>
+      </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr">
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL42" t="n">
+      <c r="AM42" t="n">
         <v>-0.179</v>
       </c>
-      <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr">
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr">
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS42" t="inlineStr">
+      <c r="AT42" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT42" t="inlineStr">
+      <c r="AU42" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
@@ -6533,7 +7155,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Probe set: 11732865_a_at; closest gene: MS4A6A</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -6566,12 +7192,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>IGAP;ADNI</t>
+          <t>ADGC;ADNI;IGAP</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6601,11 +7227,15 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>AD association</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>rs983392</t>
@@ -6616,39 +7246,44 @@
       <c r="AC43" t="n">
         <v>0.68</v>
       </c>
-      <c r="AD43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>AD association P-value</t>
+        </is>
+      </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr">
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr">
         <is>
           <t>30448613</t>
         </is>
       </c>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr">
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS43" t="inlineStr">
+      <c r="AT43" t="inlineStr">
         <is>
           <t>30448613_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT43" t="inlineStr">
+      <c r="AU43" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>

--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT22"/>
+  <dimension ref="A1:AT43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,7 +685,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -708,22 +708,30 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
@@ -734,7 +742,7 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.28</v>
+        <v>1.51e-07</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -751,11 +759,7 @@
       <c r="AL2" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
@@ -809,7 +813,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -822,7 +826,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -832,22 +836,30 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
@@ -858,7 +870,7 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -872,14 +884,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL3" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
@@ -911,7 +917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -933,7 +939,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -946,7 +952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -956,33 +962,41 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.91</v>
+        <v>2.05e-06</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -997,13 +1011,9 @@
         </is>
       </c>
       <c r="AL4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
@@ -1028,14 +1038,14 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1057,7 +1067,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1070,7 +1080,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1080,33 +1090,41 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>rs111418223</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1120,14 +1138,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL5" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
@@ -1152,7 +1164,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>BIN1</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1193,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1194,7 +1206,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1204,22 +1216,30 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
@@ -1230,7 +1250,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.83e-11</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1245,13 +1265,9 @@
         </is>
       </c>
       <c r="AL6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
@@ -1283,7 +1299,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1305,7 +1321,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1318,7 +1334,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1328,33 +1344,41 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1368,14 +1392,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL7" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
@@ -1400,14 +1418,14 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1447,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1442,7 +1460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1452,33 +1470,41 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.95</v>
+        <v>6.960000000000001e-09</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
@@ -1493,13 +1519,9 @@
         </is>
       </c>
       <c r="AL8" t="n">
-        <v>-0.129</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
+        <v>0.114</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
@@ -1524,14 +1546,14 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1553,7 +1575,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1566,7 +1588,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1576,33 +1598,41 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -1616,14 +1646,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL9" t="n">
-        <v>-0.115</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
@@ -1648,14 +1672,14 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1677,7 +1701,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1690,7 +1714,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1700,33 +1724,41 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.78</v>
+        <v>1.71e-08</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -1741,13 +1773,9 @@
         </is>
       </c>
       <c r="AL10" t="n">
-        <v>-0.107</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
+        <v>0.119</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
@@ -1772,14 +1800,14 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1801,7 +1829,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1814,7 +1842,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1824,33 +1852,41 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>rs1476679</t>
+          <t>rs111418223</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -1864,14 +1900,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL11" t="n">
-        <v>-0.128</v>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
@@ -1896,7 +1926,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>AGPAT1</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1955,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1938,7 +1968,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1948,22 +1978,30 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
@@ -1974,7 +2012,7 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.15</v>
+        <v>1.53e-17</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -1989,13 +2027,9 @@
         </is>
       </c>
       <c r="AL12" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
+        <v>0.177</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
@@ -2020,7 +2054,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2083,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2062,7 +2096,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2072,22 +2106,30 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
@@ -2098,7 +2140,7 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.82</v>
+        <v>0.53</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -2112,14 +2154,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL13" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
@@ -2144,14 +2180,14 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>GATS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2173,7 +2209,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2186,7 +2222,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2196,33 +2232,41 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.4</v>
+        <v>3.53e-09</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
@@ -2237,13 +2281,9 @@
         </is>
       </c>
       <c r="AL14" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
+        <v>-0.129</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
@@ -2268,14 +2308,14 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>LOC154761</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2297,7 +2337,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2310,7 +2350,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2320,33 +2360,41 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>0.4</v>
+        <v>0.95</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
@@ -2360,14 +2408,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL15" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr">
@@ -2392,14 +2434,14 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>TRIM4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2421,7 +2463,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2434,7 +2476,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2444,33 +2486,41 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.91</v>
+        <v>4.150000000000001e-09</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
@@ -2485,13 +2535,9 @@
         </is>
       </c>
       <c r="AL16" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
+        <v>-0.115</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr">
@@ -2516,14 +2562,14 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2545,7 +2591,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2558,7 +2604,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2568,33 +2614,41 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.47</v>
+        <v>0.85</v>
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
@@ -2608,14 +2662,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL17" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr">
@@ -2640,14 +2688,14 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2669,7 +2717,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2682,7 +2730,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2692,33 +2740,41 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>rs28834970</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.45</v>
+        <v>1.58e-08</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
@@ -2733,13 +2789,9 @@
         </is>
       </c>
       <c r="AL18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
+        <v>-0.107</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
@@ -2764,14 +2816,14 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>TRIM35</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2793,7 +2845,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2806,7 +2858,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2816,33 +2868,41 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>8.130000000000001e-05</v>
+        <v>0.78</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
@@ -2856,14 +2916,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL19" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>8.13×10 −5</t>
-        </is>
-      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr">
@@ -2888,14 +2942,14 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>MYBPC3</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2917,7 +2971,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2930,7 +2984,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2940,33 +2994,41 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.00497</v>
+        <v>3.77e-08</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
@@ -2981,13 +3043,9 @@
         </is>
       </c>
       <c r="AL20" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>4.97×10 −3</t>
-        </is>
-      </c>
+        <v>-0.128</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr">
@@ -3012,14 +3070,14 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3041,7 +3099,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3054,7 +3112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -3064,33 +3122,41 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
@@ -3104,14 +3170,8 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL21" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
@@ -3136,14 +3196,14 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>MS4A4A</t>
+          <t>PILRB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3165,7 +3225,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Discovery + IGAP + Meta-analysis</t>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3178,7 +3238,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CHARGE + ADSP + UKBB + UKBEC + ADGC + ADNI + NABEC + IGAP</t>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -3188,33 +3248,41 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Haplotype Reference Consortium + HRC;1000G + UK10K + 1000 Genomes + TOPMed</t>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>ADSP + ADGC + European + EUR + IGAP + European ancestry</t>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>AD + Alzheimer's disease</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>rs983392</t>
+          <t>rs1476679</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.68</v>
+        <v>2.3e-07</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
@@ -3229,13 +3297,9 @@
         </is>
       </c>
       <c r="AL22" t="n">
-        <v>-0.179</v>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
+        <v>0.147</v>
+      </c>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr">
@@ -3259,6 +3323,2672 @@
         </is>
       </c>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>6.07e-05</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>PVRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>3.68e-06</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>6.86e-18</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1.18e-17</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>7.33e-12</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00033</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>2.31e-06</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00034</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>rs28834970</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>TRIM35</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>1.07e-07</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>8.130000000000001e-05</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>2.34e-12</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL38" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>MS4A6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00039</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1.15e-06</v>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL40" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00041</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>1.59e-06</v>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL42" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30448613_table2_R00042</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>30448613_table2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>AD association</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>rs983392</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>30448613</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>PMC6331247</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>30448613_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>

--- a/harmonized_tables_advp/from_30448613_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_30448613_table2_v1.xlsx
@@ -685,7 +685,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -836,12 +836,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -939,7 +939,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -962,12 +962,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1067,7 +1067,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1193,7 +1193,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1216,12 +1216,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1321,7 +1321,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1344,12 +1344,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1575,7 +1575,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1598,12 +1598,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1701,7 +1701,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1724,12 +1724,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1829,7 +1829,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1852,12 +1852,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1955,7 +1955,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1978,12 +1978,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2083,7 +2083,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2232,12 +2232,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2360,12 +2360,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2463,7 +2463,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2591,7 +2591,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2614,12 +2614,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2717,7 +2717,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2845,7 +2845,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2868,12 +2868,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2971,7 +2971,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2994,12 +2994,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -3122,12 +3122,12 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3225,7 +3225,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -3248,12 +3248,12 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3353,7 +3353,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -3376,12 +3376,12 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3479,7 +3479,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -3502,12 +3502,12 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3607,7 +3607,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3630,12 +3630,12 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3733,7 +3733,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -3756,12 +3756,12 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3861,7 +3861,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3884,12 +3884,12 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3987,7 +3987,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -4010,12 +4010,12 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4115,7 +4115,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -4138,12 +4138,12 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4241,7 +4241,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -4264,12 +4264,12 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4369,7 +4369,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -4392,12 +4392,12 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4495,7 +4495,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -4518,12 +4518,12 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4623,7 +4623,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -4772,12 +4772,12 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4877,7 +4877,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -4900,12 +4900,12 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -5026,12 +5026,12 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5131,7 +5131,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -5154,12 +5154,12 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5257,7 +5257,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -5280,12 +5280,12 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5385,7 +5385,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -5408,12 +5408,12 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5511,7 +5511,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -5534,12 +5534,12 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5639,7 +5639,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -5662,12 +5662,12 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5765,7 +5765,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -5788,12 +5788,12 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5893,7 +5893,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>n + v + - + p + m + d + s + a + e +   + o + l + + + M + y + i + t + c + r</t>
+          <t>e + a + l + + + o + - +   + p + r + t + c + s + y + i + d + m + v + n</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>N +   + D + E + I + K + R + G + S + + + P + C + B + A + U + H</t>
+          <t>+ + P + N +   + G + C + D + S + E + B + A + I + K + U + H + R</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5916,12 +5916,12 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1 + R + T + P + ; + d + A + e +   + + + C + M + H + 0 + I + K + G + O + U</t>
+          <t>o + e + + + c + k + h + m + 1 + u + a +   + 0 + g + i + d + p + r + t + ;</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>n + g +   + E + y + d + o + p + u + R + t + + + c + s + a + r + e + U</t>
+          <t>e + o + a + + + p +   + r + t + c + g + u + s + y + d + n</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>h + m + z +   + d + c + 4 + l + b + 7 + i + + + 6 + s + a + r + e</t>
+          <t>a + 7 + + + e +   + 4 + r + c + z + b + h + s + i + d + l + m + 6</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
